--- a/esyluban/examples/dev/DataTables/item/道具系统表.xlsx
+++ b/esyluban/examples/dev/DataTables/item/道具系统表.xlsx
@@ -1472,7 +1472,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>full_name="item.TbItem" &amp; value_type="item.Item" &amp; comment="道具表" &amp; read_schema_from_file="false" &amp; input="通用道具表@item/道具系统表.xlsx" &amp; output="item_tbitem"</t>
+          <t>full_name="item.TbItem" &amp; comment="道具表"</t>
         </is>
       </c>
     </row>

--- a/esyluban/examples/dev/DataTables/item/道具系统表.xlsx
+++ b/esyluban/examples/dev/DataTables/item/道具系统表.xlsx
@@ -3735,7 +3735,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="R2:S2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="D4:D15 D18:D21 H4:H15 H18:H21" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
